--- a/03_김현우_Ensemble/artifacts/submissions/HUFS_validation_blend.xlsx
+++ b/03_김현우_Ensemble/artifacts/submissions/HUFS_validation_blend.xlsx
@@ -440,10 +440,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23909.32193074429</v>
+        <v>23909.56452231994</v>
       </c>
       <c r="C2" t="n">
-        <v>6.641478314095637</v>
+        <v>6.641545700644429</v>
       </c>
     </row>
     <row r="3">
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28453.6995493576</v>
+        <v>28453.87327456603</v>
       </c>
       <c r="C3" t="n">
-        <v>7.90380543037711</v>
+        <v>7.903853687379454</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48934.33688439836</v>
+        <v>48934.6125025078</v>
       </c>
       <c r="C4" t="n">
-        <v>13.59287135677732</v>
+        <v>13.59294791736328</v>
       </c>
     </row>
     <row r="5">
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34244.62950046417</v>
+        <v>34244.69180645335</v>
       </c>
       <c r="C5" t="n">
-        <v>9.512397083462268</v>
+        <v>9.512414390681487</v>
       </c>
     </row>
     <row r="6">
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1253.794241492598</v>
+        <v>1253.810130541211</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3482761781923884</v>
+        <v>0.3482805918170032</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>44812.3688282599</v>
+        <v>44812.17292414701</v>
       </c>
       <c r="C7" t="n">
-        <v>12.4478802300722</v>
+        <v>12.44782581226306</v>
       </c>
     </row>
   </sheetData>
